--- a/docs/week04/HE_Toolkit_dashboard_standard_data_template.xlsx
+++ b/docs/week04/HE_Toolkit_dashboard_standard_data_template.xlsx
@@ -1091,16 +1091,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T201"/>
-  <dataValidations count="4">
-    <dataValidation sqref="C2:C201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"HDE,NRFA,FLOWFILES,LOCAL"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"HDE,NRFA"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"HDE,NRFA"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="G2:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"HDE,NRFA"</formula1>
     </dataValidation>

--- a/docs/week04/HE_Toolkit_dashboard_standard_data_template.xlsx
+++ b/docs/week04/HE_Toolkit_dashboard_standard_data_template.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Q50 is not required; z-scores are needed for multi-site models.</t>
+          <t>Only the DC-11 Q10/Q95 flow fields are included in the default joined/model contract; z-scores are needed for multi-site models.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
